--- a/Control de caja.xlsx
+++ b/Control de caja.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\Documentos Farmavisa\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\Farmavisa_App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF4944FA-94BB-4EAA-82F1-589CE8867CE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F7087ECC-2741-412B-900A-B593BA7C7B57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="874" xr2:uid="{BEA16B71-FE3A-4F3E-BD5F-E87CB848FD8F}"/>
   </bookViews>
@@ -17,12 +17,21 @@
     <sheet name="NO TOCAR" sheetId="5" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Contro de Caja'!$A$1:$P$429</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Contro de Caja'!$A$1:$P$451</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -32,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="34">
   <si>
     <t>RESPONSABLE</t>
   </si>
@@ -1135,7 +1144,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38354C29-C222-4F2B-AFFC-CDD45F8FFA2D}">
-  <dimension ref="A1:Q440"/>
+  <dimension ref="A1:Q462"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" style="2" bestFit="1" customWidth="1"/>
@@ -18024,7 +18033,7 @@
         <v>1186000</v>
       </c>
       <c r="I306" s="9">
-        <f t="shared" ref="I306:I427" si="61">D306+H306</f>
+        <f t="shared" ref="I306:I449" si="61">D306+H306</f>
         <v>1598900</v>
       </c>
       <c r="J306" s="12">
@@ -18037,7 +18046,7 @@
         <v>0</v>
       </c>
       <c r="M306" s="20">
-        <f t="shared" ref="M306:M427" si="62">H306-J306</f>
+        <f t="shared" ref="M306:M449" si="62">H306-J306</f>
         <v>1186000</v>
       </c>
       <c r="N306" s="13">
@@ -22324,7 +22333,7 @@
         <v>27500</v>
       </c>
       <c r="H384" s="19">
-        <f t="shared" ref="H384:H427" si="64">E384+F384+G384</f>
+        <f t="shared" ref="H384:H449" si="64">E384+F384+G384</f>
         <v>360400</v>
       </c>
       <c r="I384" s="9">
@@ -22572,7 +22581,7 @@
         <v>95999</v>
       </c>
       <c r="P388" s="10">
-        <f>P430</f>
+        <f>P452</f>
         <v>0</v>
       </c>
     </row>
@@ -23836,14 +23845,14 @@
         <v>113500</v>
       </c>
       <c r="N411" s="13">
-        <f t="shared" ref="N411:N427" si="65">D411-K411</f>
+        <f t="shared" ref="N411:N449" si="65">D411-K411</f>
         <v>286700</v>
       </c>
       <c r="O411" s="12">
         <v>286700</v>
       </c>
       <c r="P411" s="10">
-        <f t="shared" ref="P411:P427" si="66">(N411-O411)*(-1)</f>
+        <f t="shared" ref="P411:P449" si="66">(N411-O411)*(-1)</f>
         <v>0</v>
       </c>
     </row>
@@ -24401,48 +24410,54 @@
       </c>
     </row>
     <row r="422" spans="1:16" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A422" s="17"/>
-      <c r="B422" s="17"/>
-      <c r="C422" s="18"/>
+      <c r="A422" s="17">
+        <v>46275</v>
+      </c>
+      <c r="B422" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="C422" s="18">
+        <v>913</v>
+      </c>
       <c r="D422" s="12">
-        <v>0</v>
+        <v>361500</v>
       </c>
       <c r="E422" s="12">
-        <v>0</v>
+        <v>45200</v>
       </c>
       <c r="F422" s="12">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="G422" s="12">
-        <v>0</v>
+        <v>236000</v>
       </c>
       <c r="H422" s="19">
         <f t="shared" si="64"/>
-        <v>0</v>
+        <v>301200</v>
       </c>
       <c r="I422" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>662700</v>
       </c>
       <c r="J422" s="12">
-        <v>0</v>
+        <v>996800</v>
       </c>
       <c r="K422" s="12">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="L422" s="12">
-        <v>0</v>
+        <v>1200000</v>
       </c>
       <c r="M422" s="20">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>-695600</v>
       </c>
       <c r="N422" s="13">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>355500</v>
       </c>
       <c r="O422" s="12">
-        <v>0</v>
+        <v>355500</v>
       </c>
       <c r="P422" s="10">
         <f t="shared" si="66"/>
@@ -24450,28 +24465,34 @@
       </c>
     </row>
     <row r="423" spans="1:16" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A423" s="17"/>
-      <c r="B423" s="17"/>
-      <c r="C423" s="18"/>
+      <c r="A423" s="17">
+        <v>46276</v>
+      </c>
+      <c r="B423" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C423" s="18">
+        <v>914</v>
+      </c>
       <c r="D423" s="12">
-        <v>0</v>
+        <v>144200</v>
       </c>
       <c r="E423" s="12">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="F423" s="12">
         <v>0</v>
       </c>
       <c r="G423" s="12">
-        <v>0</v>
+        <v>84500</v>
       </c>
       <c r="H423" s="19">
         <f t="shared" si="64"/>
-        <v>0</v>
+        <v>109500</v>
       </c>
       <c r="I423" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>253700</v>
       </c>
       <c r="J423" s="12">
         <v>0</v>
@@ -24480,18 +24501,18 @@
         <v>0</v>
       </c>
       <c r="L423" s="12">
-        <v>0</v>
+        <v>88300</v>
       </c>
       <c r="M423" s="20">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>109500</v>
       </c>
       <c r="N423" s="13">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>144200</v>
       </c>
       <c r="O423" s="12">
-        <v>0</v>
+        <v>144200</v>
       </c>
       <c r="P423" s="10">
         <f t="shared" si="66"/>
@@ -24499,28 +24520,34 @@
       </c>
     </row>
     <row r="424" spans="1:16" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A424" s="17"/>
-      <c r="B424" s="17"/>
-      <c r="C424" s="18"/>
+      <c r="A424" s="17">
+        <v>46276</v>
+      </c>
+      <c r="B424" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="C424" s="18">
+        <v>915</v>
+      </c>
       <c r="D424" s="12">
-        <v>0</v>
+        <v>297400</v>
       </c>
       <c r="E424" s="12">
-        <v>0</v>
+        <v>74200</v>
       </c>
       <c r="F424" s="12">
-        <v>0</v>
+        <v>23500</v>
       </c>
       <c r="G424" s="12">
-        <v>0</v>
+        <v>73700</v>
       </c>
       <c r="H424" s="19">
         <f t="shared" si="64"/>
-        <v>0</v>
+        <v>171400</v>
       </c>
       <c r="I424" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>468800</v>
       </c>
       <c r="J424" s="12">
         <v>0</v>
@@ -24529,18 +24556,18 @@
         <v>0</v>
       </c>
       <c r="L424" s="12">
-        <v>0</v>
+        <v>26000</v>
       </c>
       <c r="M424" s="20">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>171400</v>
       </c>
       <c r="N424" s="13">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>297400</v>
       </c>
       <c r="O424" s="12">
-        <v>0</v>
+        <v>297400</v>
       </c>
       <c r="P424" s="10">
         <f t="shared" si="66"/>
@@ -24548,48 +24575,54 @@
       </c>
     </row>
     <row r="425" spans="1:16" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A425" s="17"/>
-      <c r="B425" s="17"/>
-      <c r="C425" s="18"/>
+      <c r="A425" s="17">
+        <v>46277</v>
+      </c>
+      <c r="B425" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C425" s="18">
+        <v>916</v>
+      </c>
       <c r="D425" s="12">
-        <v>0</v>
+        <v>586800</v>
       </c>
       <c r="E425" s="12">
-        <v>0</v>
+        <v>210000</v>
       </c>
       <c r="F425" s="12">
         <v>0</v>
       </c>
       <c r="G425" s="12">
-        <v>0</v>
+        <v>275800</v>
       </c>
       <c r="H425" s="19">
         <f t="shared" si="64"/>
-        <v>0</v>
+        <v>485800</v>
       </c>
       <c r="I425" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>1072600</v>
       </c>
       <c r="J425" s="12">
         <v>0</v>
       </c>
       <c r="K425" s="12">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="L425" s="12">
         <v>0</v>
       </c>
       <c r="M425" s="20">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>485800</v>
       </c>
       <c r="N425" s="13">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>571800</v>
       </c>
       <c r="O425" s="12">
-        <v>0</v>
+        <v>571800</v>
       </c>
       <c r="P425" s="10">
         <f t="shared" si="66"/>
@@ -24597,48 +24630,54 @@
       </c>
     </row>
     <row r="426" spans="1:16" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A426" s="17"/>
-      <c r="B426" s="17"/>
-      <c r="C426" s="18"/>
+      <c r="A426" s="17">
+        <v>46278</v>
+      </c>
+      <c r="B426" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="C426" s="18">
+        <v>917</v>
+      </c>
       <c r="D426" s="12">
-        <v>0</v>
+        <v>266500</v>
       </c>
       <c r="E426" s="12">
-        <v>0</v>
+        <v>270000</v>
       </c>
       <c r="F426" s="12">
-        <v>0</v>
+        <v>341700</v>
       </c>
       <c r="G426" s="12">
-        <v>0</v>
+        <v>129700</v>
       </c>
       <c r="H426" s="19">
         <f t="shared" si="64"/>
-        <v>0</v>
+        <v>741400</v>
       </c>
       <c r="I426" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>1007900</v>
       </c>
       <c r="J426" s="12">
         <v>0</v>
       </c>
       <c r="K426" s="12">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="L426" s="12">
-        <v>0</v>
+        <v>37000</v>
       </c>
       <c r="M426" s="20">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>741400</v>
       </c>
       <c r="N426" s="13">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>262500</v>
       </c>
       <c r="O426" s="12">
-        <v>0</v>
+        <v>262500</v>
       </c>
       <c r="P426" s="10">
         <f t="shared" si="66"/>
@@ -24646,50 +24685,56 @@
       </c>
     </row>
     <row r="427" spans="1:16" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A427" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B427" s="17"/>
-      <c r="C427" s="18"/>
+      <c r="A427" s="17">
+        <v>46279</v>
+      </c>
+      <c r="B427" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="C427" s="18">
+        <v>918</v>
+      </c>
       <c r="D427" s="12">
-        <v>0</v>
+        <v>232900</v>
       </c>
       <c r="E427" s="12">
-        <v>0</v>
+        <v>28000</v>
       </c>
       <c r="F427" s="12">
-        <v>0</v>
+        <v>376000</v>
       </c>
       <c r="G427" s="12">
-        <v>0</v>
+        <v>72100</v>
       </c>
       <c r="H427" s="19">
         <f t="shared" si="64"/>
-        <v>0</v>
+        <v>476100</v>
       </c>
       <c r="I427" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>709000</v>
       </c>
       <c r="J427" s="12">
-        <v>0</v>
+        <f>493392+1372744</f>
+        <v>1866136</v>
       </c>
       <c r="K427" s="12">
         <v>0</v>
       </c>
       <c r="L427" s="12">
-        <v>0</v>
+        <f>50000+160000</f>
+        <v>210000</v>
       </c>
       <c r="M427" s="20">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>-1390036</v>
       </c>
       <c r="N427" s="13">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>232900</v>
       </c>
       <c r="O427" s="12">
-        <v>0</v>
+        <v>232900</v>
       </c>
       <c r="P427" s="10">
         <f t="shared" si="66"/>
@@ -24697,139 +24742,1319 @@
       </c>
     </row>
     <row r="428" spans="1:16" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A428" s="17"/>
-      <c r="B428" s="17"/>
-      <c r="C428" s="18"/>
+      <c r="A428" s="17">
+        <v>46279</v>
+      </c>
+      <c r="B428" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C428" s="18">
+        <v>919</v>
+      </c>
       <c r="D428" s="12">
-        <v>0</v>
+        <v>246300</v>
       </c>
       <c r="E428" s="12">
-        <v>0</v>
+        <v>140200</v>
       </c>
       <c r="F428" s="12">
-        <v>0</v>
+        <v>338700</v>
       </c>
       <c r="G428" s="12">
-        <v>0</v>
+        <v>140200</v>
       </c>
       <c r="H428" s="19">
-        <f>SUBTOTAL(9,H2:H427)</f>
-        <v>142252874</v>
-      </c>
-      <c r="I428" s="34">
-        <f>SUBTOTAL(9,I2:I427)</f>
-        <v>295114442</v>
-      </c>
-      <c r="J428" s="15">
-        <f>SUM(J2:J427)</f>
-        <v>137240653</v>
-      </c>
-      <c r="K428" s="15">
-        <f>SUM(K2:K427)</f>
-        <v>10270589</v>
-      </c>
-      <c r="L428" s="15">
-        <f>SUM(L2:L427)</f>
-        <v>142591013</v>
-      </c>
-      <c r="M428" s="15">
-        <f>SUM(M2:M427)</f>
-        <v>2782221</v>
-      </c>
-      <c r="N428" s="15">
-        <f>(SUM(N2:N427))-L428</f>
-        <v>1257134</v>
-      </c>
-      <c r="O428" s="15">
-        <f>SUM(O2:O427)</f>
-        <v>142923805</v>
+        <f t="shared" si="64"/>
+        <v>619100</v>
+      </c>
+      <c r="I428" s="9">
+        <f t="shared" si="61"/>
+        <v>865400</v>
+      </c>
+      <c r="J428" s="12">
+        <v>0</v>
+      </c>
+      <c r="K428" s="12">
+        <v>0</v>
+      </c>
+      <c r="L428" s="12">
+        <v>0</v>
+      </c>
+      <c r="M428" s="20">
+        <f t="shared" si="62"/>
+        <v>619100</v>
+      </c>
+      <c r="N428" s="13">
+        <f t="shared" si="65"/>
+        <v>246300</v>
+      </c>
+      <c r="O428" s="12">
+        <v>246300</v>
       </c>
       <c r="P428" s="10">
-        <f>SUM(P2:P427)</f>
-        <v>154998</v>
-      </c>
-    </row>
-    <row r="429" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B429" s="14"/>
-      <c r="C429" s="14"/>
-      <c r="D429" s="14"/>
-      <c r="E429" s="14"/>
-      <c r="F429" s="14"/>
-      <c r="G429" s="14"/>
-      <c r="H429" s="14"/>
-      <c r="I429" s="14"/>
-      <c r="J429" s="14"/>
-      <c r="K429" s="14"/>
-      <c r="M429" s="41">
-        <f>SUM(M428:N428)</f>
-        <v>4039355</v>
-      </c>
-      <c r="N429" s="41"/>
-      <c r="O429" s="4"/>
-    </row>
-    <row r="430" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B430" s="6"/>
-      <c r="C430" s="6"/>
-      <c r="H430" s="5"/>
-      <c r="J430" s="4"/>
-      <c r="K430" s="4"/>
-      <c r="L430" s="4"/>
-      <c r="M430" s="4"/>
-      <c r="N430" s="4"/>
-      <c r="O430" s="4"/>
-    </row>
-    <row r="431" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A431" s="6"/>
-      <c r="G431" s="6" t="s">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429" spans="1:16" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A429" s="17">
+        <v>46280</v>
+      </c>
+      <c r="B429" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="C429" s="18">
+        <v>920</v>
+      </c>
+      <c r="D429" s="12">
+        <v>211100</v>
+      </c>
+      <c r="E429" s="12">
+        <v>34000</v>
+      </c>
+      <c r="F429" s="12">
+        <v>117000</v>
+      </c>
+      <c r="G429" s="12">
+        <v>264000</v>
+      </c>
+      <c r="H429" s="19">
+        <f t="shared" si="64"/>
+        <v>415000</v>
+      </c>
+      <c r="I429" s="9">
+        <f t="shared" si="61"/>
+        <v>626100</v>
+      </c>
+      <c r="J429" s="12">
+        <v>0</v>
+      </c>
+      <c r="K429" s="12">
+        <v>0</v>
+      </c>
+      <c r="L429" s="12">
+        <f>150000+80000+121900</f>
+        <v>351900</v>
+      </c>
+      <c r="M429" s="20">
+        <f t="shared" si="62"/>
+        <v>415000</v>
+      </c>
+      <c r="N429" s="13">
+        <f t="shared" si="65"/>
+        <v>211100</v>
+      </c>
+      <c r="O429" s="12">
+        <v>211100</v>
+      </c>
+      <c r="P429" s="10">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430" spans="1:16" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A430" s="17">
+        <v>46280</v>
+      </c>
+      <c r="B430" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C430" s="18">
+        <v>921</v>
+      </c>
+      <c r="D430" s="12">
+        <v>169100</v>
+      </c>
+      <c r="E430" s="12">
+        <v>93200</v>
+      </c>
+      <c r="F430" s="12">
+        <v>13500</v>
+      </c>
+      <c r="G430" s="12">
+        <v>95500</v>
+      </c>
+      <c r="H430" s="19">
+        <f t="shared" si="64"/>
+        <v>202200</v>
+      </c>
+      <c r="I430" s="9">
+        <f t="shared" si="61"/>
+        <v>371300</v>
+      </c>
+      <c r="J430" s="12">
+        <v>185038</v>
+      </c>
+      <c r="K430" s="12">
+        <v>0</v>
+      </c>
+      <c r="L430" s="12">
+        <v>0</v>
+      </c>
+      <c r="M430" s="20">
+        <f t="shared" si="62"/>
+        <v>17162</v>
+      </c>
+      <c r="N430" s="13">
+        <f t="shared" si="65"/>
+        <v>169100</v>
+      </c>
+      <c r="O430" s="12">
+        <v>169100</v>
+      </c>
+      <c r="P430" s="10">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="431" spans="1:16" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A431" s="17">
+        <v>46281</v>
+      </c>
+      <c r="B431" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="C431" s="18">
+        <v>922</v>
+      </c>
+      <c r="D431" s="12">
+        <v>164500</v>
+      </c>
+      <c r="E431" s="12">
+        <v>57000</v>
+      </c>
+      <c r="F431" s="12">
+        <v>0</v>
+      </c>
+      <c r="G431" s="12">
+        <v>209000</v>
+      </c>
+      <c r="H431" s="19">
+        <f t="shared" si="64"/>
+        <v>266000</v>
+      </c>
+      <c r="I431" s="9">
+        <f t="shared" si="61"/>
+        <v>430500</v>
+      </c>
+      <c r="J431" s="12">
+        <v>0</v>
+      </c>
+      <c r="K431" s="12">
+        <v>0</v>
+      </c>
+      <c r="L431" s="12">
+        <v>0</v>
+      </c>
+      <c r="M431" s="20">
+        <f t="shared" si="62"/>
+        <v>266000</v>
+      </c>
+      <c r="N431" s="13">
+        <f t="shared" si="65"/>
+        <v>164500</v>
+      </c>
+      <c r="O431" s="12">
+        <v>164500</v>
+      </c>
+      <c r="P431" s="10">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="432" spans="1:16" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A432" s="17">
+        <v>46281</v>
+      </c>
+      <c r="B432" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C432" s="18">
+        <v>923</v>
+      </c>
+      <c r="D432" s="12">
+        <v>251300</v>
+      </c>
+      <c r="E432" s="12">
+        <v>89000</v>
+      </c>
+      <c r="F432" s="12">
+        <v>0</v>
+      </c>
+      <c r="G432" s="12">
+        <v>18500</v>
+      </c>
+      <c r="H432" s="19">
+        <f t="shared" si="64"/>
+        <v>107500</v>
+      </c>
+      <c r="I432" s="9">
+        <f t="shared" si="61"/>
+        <v>358800</v>
+      </c>
+      <c r="J432" s="12">
+        <v>0</v>
+      </c>
+      <c r="K432" s="12">
+        <v>0</v>
+      </c>
+      <c r="L432" s="12">
+        <v>0</v>
+      </c>
+      <c r="M432" s="20">
+        <f t="shared" si="62"/>
+        <v>107500</v>
+      </c>
+      <c r="N432" s="13">
+        <f t="shared" si="65"/>
+        <v>251300</v>
+      </c>
+      <c r="O432" s="12">
+        <v>251300</v>
+      </c>
+      <c r="P432" s="10">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433" spans="1:16" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A433" s="17">
+        <v>46282</v>
+      </c>
+      <c r="B433" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C433" s="18">
+        <v>924</v>
+      </c>
+      <c r="D433" s="12">
+        <v>283700</v>
+      </c>
+      <c r="E433" s="12">
+        <v>94500</v>
+      </c>
+      <c r="F433" s="12">
+        <v>0</v>
+      </c>
+      <c r="G433" s="12">
+        <v>10600</v>
+      </c>
+      <c r="H433" s="19">
+        <f t="shared" si="64"/>
+        <v>105100</v>
+      </c>
+      <c r="I433" s="9">
+        <f t="shared" si="61"/>
+        <v>388800</v>
+      </c>
+      <c r="J433" s="12">
+        <v>0</v>
+      </c>
+      <c r="K433" s="12">
+        <v>44000</v>
+      </c>
+      <c r="L433" s="12">
+        <v>0</v>
+      </c>
+      <c r="M433" s="20">
+        <f t="shared" si="62"/>
+        <v>105100</v>
+      </c>
+      <c r="N433" s="13">
+        <f t="shared" si="65"/>
+        <v>239700</v>
+      </c>
+      <c r="O433" s="12">
+        <v>239800</v>
+      </c>
+      <c r="P433" s="10">
+        <f t="shared" si="66"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="434" spans="1:16" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A434" s="17">
+        <v>46282</v>
+      </c>
+      <c r="B434" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="C434" s="18">
+        <v>925</v>
+      </c>
+      <c r="D434" s="12">
+        <v>153400</v>
+      </c>
+      <c r="E434" s="12">
+        <v>29000</v>
+      </c>
+      <c r="F434" s="12">
+        <v>0</v>
+      </c>
+      <c r="G434" s="12">
+        <v>592000</v>
+      </c>
+      <c r="H434" s="19">
+        <f t="shared" si="64"/>
+        <v>621000</v>
+      </c>
+      <c r="I434" s="9">
+        <f t="shared" si="61"/>
+        <v>774400</v>
+      </c>
+      <c r="J434" s="12">
+        <v>0</v>
+      </c>
+      <c r="K434" s="12">
+        <v>0</v>
+      </c>
+      <c r="L434" s="12">
+        <v>295000</v>
+      </c>
+      <c r="M434" s="20">
+        <f t="shared" si="62"/>
+        <v>621000</v>
+      </c>
+      <c r="N434" s="13">
+        <f t="shared" si="65"/>
+        <v>153400</v>
+      </c>
+      <c r="O434" s="12">
+        <v>153400</v>
+      </c>
+      <c r="P434" s="10">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="435" spans="1:16" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A435" s="17">
+        <v>46283</v>
+      </c>
+      <c r="B435" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="C435" s="18">
+        <v>926</v>
+      </c>
+      <c r="D435" s="12">
+        <v>264100</v>
+      </c>
+      <c r="E435" s="12">
+        <v>30000</v>
+      </c>
+      <c r="F435" s="12">
+        <v>558800</v>
+      </c>
+      <c r="G435" s="12">
+        <v>344500</v>
+      </c>
+      <c r="H435" s="19">
+        <f t="shared" si="64"/>
+        <v>933300</v>
+      </c>
+      <c r="I435" s="9">
+        <f t="shared" si="61"/>
+        <v>1197400</v>
+      </c>
+      <c r="J435" s="12">
+        <v>0</v>
+      </c>
+      <c r="K435" s="12">
+        <v>4400</v>
+      </c>
+      <c r="L435" s="12">
+        <f>92400+113900</f>
+        <v>206300</v>
+      </c>
+      <c r="M435" s="20">
+        <f t="shared" si="62"/>
+        <v>933300</v>
+      </c>
+      <c r="N435" s="13">
+        <f t="shared" si="65"/>
+        <v>259700</v>
+      </c>
+      <c r="O435" s="12">
+        <v>260000</v>
+      </c>
+      <c r="P435" s="10">
+        <f t="shared" si="66"/>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="436" spans="1:16" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A436" s="17">
+        <v>46283</v>
+      </c>
+      <c r="B436" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C436" s="18">
+        <v>927</v>
+      </c>
+      <c r="D436" s="12">
+        <v>192200</v>
+      </c>
+      <c r="E436" s="12">
+        <v>225300</v>
+      </c>
+      <c r="F436" s="12">
+        <v>54000</v>
+      </c>
+      <c r="G436" s="12">
+        <v>157500</v>
+      </c>
+      <c r="H436" s="19">
+        <f t="shared" si="64"/>
+        <v>436800</v>
+      </c>
+      <c r="I436" s="9">
+        <f t="shared" si="61"/>
+        <v>629000</v>
+      </c>
+      <c r="J436" s="12">
+        <v>0</v>
+      </c>
+      <c r="K436" s="12">
+        <v>3000</v>
+      </c>
+      <c r="L436" s="12">
+        <v>0</v>
+      </c>
+      <c r="M436" s="20">
+        <f t="shared" si="62"/>
+        <v>436800</v>
+      </c>
+      <c r="N436" s="13">
+        <f t="shared" si="65"/>
+        <v>189200</v>
+      </c>
+      <c r="O436" s="12">
+        <v>189200</v>
+      </c>
+      <c r="P436" s="10">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="437" spans="1:16" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A437" s="17">
+        <v>46284</v>
+      </c>
+      <c r="B437" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C437" s="18">
+        <v>928</v>
+      </c>
+      <c r="D437" s="12">
+        <v>313600</v>
+      </c>
+      <c r="E437" s="12">
+        <v>131100</v>
+      </c>
+      <c r="F437" s="12">
+        <v>0</v>
+      </c>
+      <c r="G437" s="12">
+        <v>238500</v>
+      </c>
+      <c r="H437" s="19">
+        <f t="shared" si="64"/>
+        <v>369600</v>
+      </c>
+      <c r="I437" s="9">
+        <f t="shared" si="61"/>
+        <v>683200</v>
+      </c>
+      <c r="J437" s="12">
+        <v>0</v>
+      </c>
+      <c r="K437" s="12">
+        <v>4000</v>
+      </c>
+      <c r="L437" s="12">
+        <v>0</v>
+      </c>
+      <c r="M437" s="20">
+        <f t="shared" si="62"/>
+        <v>369600</v>
+      </c>
+      <c r="N437" s="13">
+        <f t="shared" si="65"/>
+        <v>309600</v>
+      </c>
+      <c r="O437" s="12">
+        <v>309600</v>
+      </c>
+      <c r="P437" s="10">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="438" spans="1:16" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A438" s="17">
+        <v>46285</v>
+      </c>
+      <c r="B438" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="C438" s="18">
+        <v>929</v>
+      </c>
+      <c r="D438" s="12">
+        <v>509600</v>
+      </c>
+      <c r="E438" s="12">
+        <v>87100</v>
+      </c>
+      <c r="F438" s="12">
+        <v>54000</v>
+      </c>
+      <c r="G438" s="12">
+        <v>62100</v>
+      </c>
+      <c r="H438" s="19">
+        <f t="shared" si="64"/>
+        <v>203200</v>
+      </c>
+      <c r="I438" s="9">
+        <f t="shared" si="61"/>
+        <v>712800</v>
+      </c>
+      <c r="J438" s="12">
+        <v>0</v>
+      </c>
+      <c r="K438" s="12">
+        <v>0</v>
+      </c>
+      <c r="L438" s="12">
+        <v>46200</v>
+      </c>
+      <c r="M438" s="20">
+        <f t="shared" si="62"/>
+        <v>203200</v>
+      </c>
+      <c r="N438" s="13">
+        <f t="shared" si="65"/>
+        <v>509600</v>
+      </c>
+      <c r="O438" s="12">
+        <v>509600</v>
+      </c>
+      <c r="P438" s="10">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="439" spans="1:16" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A439" s="17">
+        <v>46286</v>
+      </c>
+      <c r="B439" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C439" s="18">
+        <v>930</v>
+      </c>
+      <c r="D439" s="12">
+        <v>148100</v>
+      </c>
+      <c r="E439" s="12">
+        <v>0</v>
+      </c>
+      <c r="F439" s="12">
+        <v>0</v>
+      </c>
+      <c r="G439" s="12">
+        <v>47000</v>
+      </c>
+      <c r="H439" s="19">
+        <f t="shared" si="64"/>
+        <v>47000</v>
+      </c>
+      <c r="I439" s="9">
+        <f t="shared" si="61"/>
+        <v>195100</v>
+      </c>
+      <c r="J439" s="12">
+        <v>0</v>
+      </c>
+      <c r="K439" s="12">
+        <v>0</v>
+      </c>
+      <c r="L439" s="12">
+        <v>0</v>
+      </c>
+      <c r="M439" s="20">
+        <f t="shared" si="62"/>
+        <v>47000</v>
+      </c>
+      <c r="N439" s="13">
+        <f t="shared" si="65"/>
+        <v>148100</v>
+      </c>
+      <c r="O439" s="12">
+        <v>148100</v>
+      </c>
+      <c r="P439" s="10">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="440" spans="1:16" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A440" s="17">
+        <v>46286</v>
+      </c>
+      <c r="B440" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="C440" s="18">
+        <v>931</v>
+      </c>
+      <c r="D440" s="12">
+        <v>323700</v>
+      </c>
+      <c r="E440" s="12">
+        <v>38200</v>
+      </c>
+      <c r="F440" s="12">
+        <v>401000</v>
+      </c>
+      <c r="G440" s="12">
+        <v>89500</v>
+      </c>
+      <c r="H440" s="19">
+        <f t="shared" si="64"/>
+        <v>528700</v>
+      </c>
+      <c r="I440" s="9">
+        <f t="shared" si="61"/>
+        <v>852400</v>
+      </c>
+      <c r="J440" s="12">
+        <v>2751750</v>
+      </c>
+      <c r="K440" s="12">
+        <v>2000</v>
+      </c>
+      <c r="L440" s="12">
+        <f>2866300+34000</f>
+        <v>2900300</v>
+      </c>
+      <c r="M440" s="20">
+        <f t="shared" si="62"/>
+        <v>-2223050</v>
+      </c>
+      <c r="N440" s="13">
+        <f t="shared" si="65"/>
+        <v>321700</v>
+      </c>
+      <c r="O440" s="12">
+        <v>321700</v>
+      </c>
+      <c r="P440" s="10">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="441" spans="1:16" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A441" s="17">
+        <v>46287</v>
+      </c>
+      <c r="B441" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C441" s="18">
+        <v>932</v>
+      </c>
+      <c r="D441" s="12">
+        <v>404400</v>
+      </c>
+      <c r="E441" s="12">
+        <v>35100</v>
+      </c>
+      <c r="F441" s="12">
+        <v>10400</v>
+      </c>
+      <c r="G441" s="12">
+        <v>122000</v>
+      </c>
+      <c r="H441" s="19">
+        <f t="shared" si="64"/>
+        <v>167500</v>
+      </c>
+      <c r="I441" s="9">
+        <f t="shared" si="61"/>
+        <v>571900</v>
+      </c>
+      <c r="J441" s="12">
+        <v>0</v>
+      </c>
+      <c r="K441" s="12">
+        <v>338906</v>
+      </c>
+      <c r="L441" s="12">
+        <v>0</v>
+      </c>
+      <c r="M441" s="20">
+        <f t="shared" si="62"/>
+        <v>167500</v>
+      </c>
+      <c r="N441" s="13">
+        <f t="shared" si="65"/>
+        <v>65494</v>
+      </c>
+      <c r="O441" s="12">
+        <v>65500</v>
+      </c>
+      <c r="P441" s="10">
+        <f t="shared" si="66"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="442" spans="1:16" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A442" s="17">
+        <v>46287</v>
+      </c>
+      <c r="B442" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="C442" s="18">
+        <v>933</v>
+      </c>
+      <c r="D442" s="12">
+        <v>215100</v>
+      </c>
+      <c r="E442" s="12">
+        <v>159100</v>
+      </c>
+      <c r="F442" s="12">
+        <v>75000</v>
+      </c>
+      <c r="G442" s="12">
+        <v>303500</v>
+      </c>
+      <c r="H442" s="19">
+        <f t="shared" si="64"/>
+        <v>537600</v>
+      </c>
+      <c r="I442" s="9">
+        <f t="shared" si="61"/>
+        <v>752700</v>
+      </c>
+      <c r="J442" s="12">
+        <v>1317776</v>
+      </c>
+      <c r="K442" s="12">
+        <v>2000</v>
+      </c>
+      <c r="L442" s="12">
+        <f>76000+838350</f>
+        <v>914350</v>
+      </c>
+      <c r="M442" s="20">
+        <f t="shared" si="62"/>
+        <v>-780176</v>
+      </c>
+      <c r="N442" s="13">
+        <f t="shared" si="65"/>
+        <v>213100</v>
+      </c>
+      <c r="O442" s="12">
+        <v>213100</v>
+      </c>
+      <c r="P442" s="10">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="443" spans="1:16" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A443" s="17">
+        <v>46288</v>
+      </c>
+      <c r="B443" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C443" s="18">
+        <v>934</v>
+      </c>
+      <c r="D443" s="12">
+        <v>197100</v>
+      </c>
+      <c r="E443" s="12">
+        <v>34500</v>
+      </c>
+      <c r="F443" s="12">
+        <v>0</v>
+      </c>
+      <c r="G443" s="12">
+        <v>20000</v>
+      </c>
+      <c r="H443" s="19">
+        <f t="shared" si="64"/>
+        <v>54500</v>
+      </c>
+      <c r="I443" s="9">
+        <f t="shared" si="61"/>
+        <v>251600</v>
+      </c>
+      <c r="J443" s="12">
+        <v>0</v>
+      </c>
+      <c r="K443" s="12">
+        <v>0</v>
+      </c>
+      <c r="L443" s="12">
+        <v>0</v>
+      </c>
+      <c r="M443" s="20">
+        <f t="shared" si="62"/>
+        <v>54500</v>
+      </c>
+      <c r="N443" s="13">
+        <f t="shared" si="65"/>
+        <v>197100</v>
+      </c>
+      <c r="O443" s="12">
+        <v>197100</v>
+      </c>
+      <c r="P443" s="10">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="444" spans="1:16" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A444" s="17"/>
+      <c r="B444" s="17"/>
+      <c r="C444" s="18"/>
+      <c r="D444" s="12">
+        <v>0</v>
+      </c>
+      <c r="E444" s="12">
+        <v>0</v>
+      </c>
+      <c r="F444" s="12">
+        <v>0</v>
+      </c>
+      <c r="G444" s="12">
+        <v>0</v>
+      </c>
+      <c r="H444" s="19">
+        <f t="shared" si="64"/>
+        <v>0</v>
+      </c>
+      <c r="I444" s="9">
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
+      <c r="J444" s="12">
+        <v>0</v>
+      </c>
+      <c r="K444" s="12">
+        <v>0</v>
+      </c>
+      <c r="L444" s="12">
+        <v>0</v>
+      </c>
+      <c r="M444" s="20">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="N444" s="13">
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+      <c r="O444" s="12">
+        <v>0</v>
+      </c>
+      <c r="P444" s="10">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="445" spans="1:16" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A445" s="17"/>
+      <c r="B445" s="17"/>
+      <c r="C445" s="18"/>
+      <c r="D445" s="12">
+        <v>0</v>
+      </c>
+      <c r="E445" s="12">
+        <v>0</v>
+      </c>
+      <c r="F445" s="12">
+        <v>0</v>
+      </c>
+      <c r="G445" s="12">
+        <v>0</v>
+      </c>
+      <c r="H445" s="19">
+        <f t="shared" si="64"/>
+        <v>0</v>
+      </c>
+      <c r="I445" s="9">
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
+      <c r="J445" s="12">
+        <v>0</v>
+      </c>
+      <c r="K445" s="12">
+        <v>0</v>
+      </c>
+      <c r="L445" s="12">
+        <v>0</v>
+      </c>
+      <c r="M445" s="20">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="N445" s="13">
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+      <c r="O445" s="12">
+        <v>0</v>
+      </c>
+      <c r="P445" s="10">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="446" spans="1:16" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A446" s="17"/>
+      <c r="B446" s="17"/>
+      <c r="C446" s="18"/>
+      <c r="D446" s="12">
+        <v>0</v>
+      </c>
+      <c r="E446" s="12">
+        <v>0</v>
+      </c>
+      <c r="F446" s="12">
+        <v>0</v>
+      </c>
+      <c r="G446" s="12">
+        <v>0</v>
+      </c>
+      <c r="H446" s="19">
+        <f t="shared" si="64"/>
+        <v>0</v>
+      </c>
+      <c r="I446" s="9">
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
+      <c r="J446" s="12">
+        <v>0</v>
+      </c>
+      <c r="K446" s="12">
+        <v>0</v>
+      </c>
+      <c r="L446" s="12">
+        <v>0</v>
+      </c>
+      <c r="M446" s="20">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="N446" s="13">
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+      <c r="O446" s="12">
+        <v>0</v>
+      </c>
+      <c r="P446" s="10">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="447" spans="1:16" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A447" s="17"/>
+      <c r="B447" s="17"/>
+      <c r="C447" s="18"/>
+      <c r="D447" s="12">
+        <v>0</v>
+      </c>
+      <c r="E447" s="12">
+        <v>0</v>
+      </c>
+      <c r="F447" s="12">
+        <v>0</v>
+      </c>
+      <c r="G447" s="12">
+        <v>0</v>
+      </c>
+      <c r="H447" s="19">
+        <f t="shared" si="64"/>
+        <v>0</v>
+      </c>
+      <c r="I447" s="9">
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
+      <c r="J447" s="12">
+        <v>0</v>
+      </c>
+      <c r="K447" s="12">
+        <v>0</v>
+      </c>
+      <c r="L447" s="12">
+        <v>0</v>
+      </c>
+      <c r="M447" s="20">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="N447" s="13">
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+      <c r="O447" s="12">
+        <v>0</v>
+      </c>
+      <c r="P447" s="10">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="448" spans="1:16" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A448" s="17"/>
+      <c r="B448" s="17"/>
+      <c r="C448" s="18"/>
+      <c r="D448" s="12">
+        <v>0</v>
+      </c>
+      <c r="E448" s="12">
+        <v>0</v>
+      </c>
+      <c r="F448" s="12">
+        <v>0</v>
+      </c>
+      <c r="G448" s="12">
+        <v>0</v>
+      </c>
+      <c r="H448" s="19">
+        <f t="shared" si="64"/>
+        <v>0</v>
+      </c>
+      <c r="I448" s="9">
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
+      <c r="J448" s="12">
+        <v>0</v>
+      </c>
+      <c r="K448" s="12">
+        <v>0</v>
+      </c>
+      <c r="L448" s="12">
+        <v>0</v>
+      </c>
+      <c r="M448" s="20">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="N448" s="13">
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+      <c r="O448" s="12">
+        <v>0</v>
+      </c>
+      <c r="P448" s="10">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="449" spans="1:16" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A449" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B449" s="17"/>
+      <c r="C449" s="18"/>
+      <c r="D449" s="12">
+        <v>0</v>
+      </c>
+      <c r="E449" s="12">
+        <v>0</v>
+      </c>
+      <c r="F449" s="12">
+        <v>0</v>
+      </c>
+      <c r="G449" s="12">
+        <v>0</v>
+      </c>
+      <c r="H449" s="19">
+        <f t="shared" si="64"/>
+        <v>0</v>
+      </c>
+      <c r="I449" s="9">
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
+      <c r="J449" s="12">
+        <v>0</v>
+      </c>
+      <c r="K449" s="12">
+        <v>0</v>
+      </c>
+      <c r="L449" s="12">
+        <v>0</v>
+      </c>
+      <c r="M449" s="20">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="N449" s="13">
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+      <c r="O449" s="12">
+        <v>0</v>
+      </c>
+      <c r="P449" s="10">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="450" spans="1:16" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A450" s="17"/>
+      <c r="B450" s="17"/>
+      <c r="C450" s="18"/>
+      <c r="D450" s="12">
+        <v>0</v>
+      </c>
+      <c r="E450" s="12">
+        <v>0</v>
+      </c>
+      <c r="F450" s="12">
+        <v>0</v>
+      </c>
+      <c r="G450" s="12">
+        <v>0</v>
+      </c>
+      <c r="H450" s="19">
+        <f>SUBTOTAL(9,H2:H449)</f>
+        <v>150152374</v>
+      </c>
+      <c r="I450" s="34">
+        <f>SUBTOTAL(9,I2:I449)</f>
+        <v>308950542</v>
+      </c>
+      <c r="J450" s="15">
+        <f>SUM(J2:J449)</f>
+        <v>144358153</v>
+      </c>
+      <c r="K450" s="15">
+        <f>SUM(K2:K449)</f>
+        <v>10693895</v>
+      </c>
+      <c r="L450" s="15">
+        <f>SUM(L2:L449)</f>
+        <v>148866363</v>
+      </c>
+      <c r="M450" s="15">
+        <f>SUM(M2:M449)</f>
+        <v>3564221</v>
+      </c>
+      <c r="N450" s="15">
+        <f>(SUM(N2:N449))-L450</f>
+        <v>495078</v>
+      </c>
+      <c r="O450" s="15">
+        <f>SUM(O2:O449)</f>
+        <v>148437505</v>
+      </c>
+      <c r="P450" s="10">
+        <f>SUM(P2:P449)</f>
+        <v>155404</v>
+      </c>
+    </row>
+    <row r="451" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B451" s="14"/>
+      <c r="C451" s="14"/>
+      <c r="D451" s="14"/>
+      <c r="E451" s="14"/>
+      <c r="F451" s="14"/>
+      <c r="G451" s="14"/>
+      <c r="H451" s="14"/>
+      <c r="I451" s="14"/>
+      <c r="J451" s="14"/>
+      <c r="K451" s="14"/>
+      <c r="M451" s="41">
+        <f>SUM(M450:N450)</f>
+        <v>4059299</v>
+      </c>
+      <c r="N451" s="41"/>
+      <c r="O451" s="4"/>
+    </row>
+    <row r="452" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B452" s="6"/>
+      <c r="C452" s="6"/>
+      <c r="H452" s="5"/>
+      <c r="J452" s="4"/>
+      <c r="K452" s="4"/>
+      <c r="L452" s="4"/>
+      <c r="M452" s="4"/>
+      <c r="N452" s="4"/>
+      <c r="O452" s="4"/>
+    </row>
+    <row r="453" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A453" s="6"/>
+      <c r="G453" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="H431" s="5"/>
-      <c r="M431" s="5"/>
-    </row>
-    <row r="432" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L432" s="5"/>
-      <c r="N432" s="7"/>
-      <c r="O432" s="4"/>
-    </row>
-    <row r="433" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K433" s="6" t="s">
+      <c r="H453" s="5"/>
+      <c r="M453" s="5"/>
+    </row>
+    <row r="454" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L454" s="5"/>
+      <c r="N454" s="7"/>
+      <c r="O454" s="4"/>
+    </row>
+    <row r="455" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K455" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="N433" s="3" t="s">
+      <c r="N455" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="434" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A434" s="4"/>
-      <c r="K434" s="6" t="s">
+    <row r="456" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A456" s="4"/>
+      <c r="K456" s="6" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="435" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A435" s="4"/>
-    </row>
-    <row r="436" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="437" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K437" s="5"/>
-    </row>
-    <row r="438" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K438" s="6" t="s">
+    <row r="457" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A457" s="4"/>
+    </row>
+    <row r="458" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K459" s="5"/>
+    </row>
+    <row r="460" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K460" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="439" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="440" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A1:P429" xr:uid="{38354C29-C222-4F2B-AFFC-CDD45F8FFA2D}"/>
+  <autoFilter ref="A1:P451" xr:uid="{38354C29-C222-4F2B-AFFC-CDD45F8FFA2D}"/>
   <mergeCells count="1">
-    <mergeCell ref="M429:N429"/>
+    <mergeCell ref="M451:N451"/>
   </mergeCells>
-  <conditionalFormatting sqref="P3:P19 P94:P128 P428">
+  <conditionalFormatting sqref="P3:P19 P94:P128 P450">
     <cfRule type="cellIs" dxfId="47" priority="270" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P3:P19 P94:P128 P428">
+  <conditionalFormatting sqref="P3:P19 P94:P128 P450">
     <cfRule type="cellIs" dxfId="46" priority="269" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
@@ -25044,12 +26269,12 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P133:P225 P227:P427">
+  <conditionalFormatting sqref="P133:P225 P227:P449">
     <cfRule type="cellIs" dxfId="3" priority="24" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P133:P225 P227:P427">
+  <conditionalFormatting sqref="P133:P225 P227:P449">
     <cfRule type="cellIs" dxfId="2" priority="23" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
@@ -25073,7 +26298,7 @@
           <x14:formula1>
             <xm:f>'NO TOCAR'!$A$1:$A$2</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B178 B183:B428</xm:sqref>
+          <xm:sqref>B2:B178 B183:B450</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
